--- a/TIMES-NZ/v303/SuppXLS/Scen_ProcessHeatCoalBan.xlsx
+++ b/TIMES-NZ/v303/SuppXLS/Scen_ProcessHeatCoalBan.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -504,12 +504,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AINDC-SH</t>
+          <t>AINDC-Boiler-SH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>COAL-BAN-AINDC-SH</t>
+          <t>COAL-BAN-AINDC-Boiler-SH</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AINDC-SH</t>
+          <t>AINDC-Boiler-SH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>COAL-BAN-AINDC-SH</t>
+          <t>COAL-BAN-AINDC-Boiler-SH</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -588,12 +588,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C_EDU-SH</t>
+          <t>C_EDU-Boiler-SH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_EDU-SH</t>
+          <t>COAL-BAN-C_EDU-Boiler-SH</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -630,12 +630,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C_EDU-SH</t>
+          <t>C_EDU-Boiler-SH</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_EDU-SH</t>
+          <t>COAL-BAN-C_EDU-Boiler-SH</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -672,12 +672,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C_EDU-WH</t>
+          <t>C_EDU-Boiler-WH</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_EDU-WH</t>
+          <t>COAL-BAN-C_EDU-Boiler-WH</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C_EDU-WH</t>
+          <t>C_EDU-Boiler-WH</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_EDU-WH</t>
+          <t>COAL-BAN-C_EDU-Boiler-WH</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C_HLTH-PH</t>
+          <t>C_HLTH-Boiler-PH</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_HLTH-PH</t>
+          <t>COAL-BAN-C_HLTH-Boiler-PH</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C_HLTH-PH</t>
+          <t>C_HLTH-Boiler-PH</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_HLTH-PH</t>
+          <t>COAL-BAN-C_HLTH-Boiler-PH</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -840,12 +840,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-Boiler-SH</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_HLTH-SH</t>
+          <t>COAL-BAN-C_HLTH-Boiler-SH</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-Boiler-SH</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_HLTH-SH</t>
+          <t>COAL-BAN-C_HLTH-Boiler-SH</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -924,12 +924,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C_HLTH-WH</t>
+          <t>C_HLTH-Boiler-WH</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_HLTH-WH</t>
+          <t>COAL-BAN-C_HLTH-Boiler-WH</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>C_HLTH-WH</t>
+          <t>C_HLTH-Boiler-WH</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_HLTH-WH</t>
+          <t>COAL-BAN-C_HLTH-Boiler-WH</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C_OFFC-SH</t>
+          <t>C_OFFC-Boiler-SH</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_OFFC-SH</t>
+          <t>COAL-BAN-C_OFFC-Boiler-SH</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C_OFFC-SH</t>
+          <t>C_OFFC-Boiler-SH</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_OFFC-SH</t>
+          <t>COAL-BAN-C_OFFC-Boiler-SH</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C_OFFC-WH</t>
+          <t>C_OFFC-Boiler-WH</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_OFFC-WH</t>
+          <t>COAL-BAN-C_OFFC-Boiler-WH</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C_OFFC-WH</t>
+          <t>C_OFFC-Boiler-WH</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_OFFC-WH</t>
+          <t>COAL-BAN-C_OFFC-Boiler-WH</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-Boiler-SH</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_OTH-SH</t>
+          <t>COAL-BAN-C_OTH-Boiler-SH</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-Boiler-SH</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_OTH-SH</t>
+          <t>COAL-BAN-C_OTH-Boiler-SH</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>C_OTH-WH</t>
+          <t>C_OTH-Boiler-WH</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_OTH-WH</t>
+          <t>COAL-BAN-C_OTH-Boiler-WH</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>C_OTH-WH</t>
+          <t>C_OTH-Boiler-WH</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_OTH-WH</t>
+          <t>COAL-BAN-C_OTH-Boiler-WH</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>C_WSR-SH</t>
+          <t>C_WSR-Boiler-SH</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_WSR-SH</t>
+          <t>COAL-BAN-C_WSR-Boiler-SH</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>C_WSR-SH</t>
+          <t>C_WSR-Boiler-SH</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_WSR-SH</t>
+          <t>COAL-BAN-C_WSR-Boiler-SH</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>C_WSR-WH</t>
+          <t>C_WSR-Boiler-WH</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_WSR-WH</t>
+          <t>COAL-BAN-C_WSR-Boiler-WH</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>C_WSR-WH</t>
+          <t>C_WSR-Boiler-WH</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>COAL-BAN-C_WSR-WH</t>
+          <t>COAL-BAN-C_WSR-Boiler-WH</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1507,17 +1507,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>-INDCOA</t>
+          <t>-COMCOA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DARY-BOILR-PH_INT</t>
+          <t>C_WSR-Burner-SH</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>COAL-BAN-DARY-BOILR-PH_INT</t>
+          <t>COAL-BAN-C_WSR-Burner-SH</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1549,17 +1549,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>INDCOA</t>
+          <t>COMCOA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DARY-BOILR-PH_INT</t>
+          <t>C_WSR-Burner-SH</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>COAL-BAN-DARY-BOILR-PH_INT</t>
+          <t>COAL-BAN-C_WSR-Burner-SH</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DARY-BOILR-PH_LOW</t>
+          <t>DARY-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>COAL-BAN-DARY-BOILR-PH_LOW</t>
+          <t>COAL-BAN-DARY-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DARY-BOILR-PH_LOW</t>
+          <t>DARY-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>COAL-BAN-DARY-BOILR-PH_LOW</t>
+          <t>COAL-BAN-DARY-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DARY-BOILR-WH_LOW</t>
+          <t>DARY-BOILR-PH_LOW</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>COAL-BAN-DARY-BOILR-WH_LOW</t>
+          <t>COAL-BAN-DARY-BOILR-PH_LOW</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DARY-BOILR-WH_LOW</t>
+          <t>DARY-BOILR-PH_LOW</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>COAL-BAN-DARY-BOILR-WH_LOW</t>
+          <t>COAL-BAN-DARY-BOILR-PH_LOW</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1759,17 +1759,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>-RESCOA</t>
+          <t>-INDCOA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DD-S_HEAT</t>
+          <t>DARY-BOILR-WH_LOW</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>COAL-BAN-DD-S_HEAT</t>
+          <t>COAL-BAN-DARY-BOILR-WH_LOW</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1801,17 +1801,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RESCOA</t>
+          <t>INDCOA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DD-S_HEAT</t>
+          <t>DARY-BOILR-WH_LOW</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>COAL-BAN-DD-S_HEAT</t>
+          <t>COAL-BAN-DARY-BOILR-WH_LOW</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1843,17 +1843,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>-INDCOA</t>
+          <t>-RESCOA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FOOD-BOILR-PH_INT</t>
+          <t>DD-S_HEAT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>COAL-BAN-FOOD-BOILR-PH_INT</t>
+          <t>COAL-BAN-DD-S_HEAT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1885,17 +1885,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>INDCOA</t>
+          <t>RESCOA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FOOD-BOILR-PH_INT</t>
+          <t>DD-S_HEAT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>COAL-BAN-FOOD-BOILR-PH_INT</t>
+          <t>COAL-BAN-DD-S_HEAT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FOOD-BOILR-PH_LOW</t>
+          <t>FOOD-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>COAL-BAN-FOOD-BOILR-PH_LOW</t>
+          <t>COAL-BAN-FOOD-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FOOD-BOILR-PH_LOW</t>
+          <t>FOOD-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>COAL-BAN-FOOD-BOILR-PH_LOW</t>
+          <t>COAL-BAN-FOOD-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FOOD-BOILR-WH_LOW</t>
+          <t>FOOD-BOILR-PH_LOW</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>COAL-BAN-FOOD-BOILR-WH_LOW</t>
+          <t>COAL-BAN-FOOD-BOILR-PH_LOW</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FOOD-BOILR-WH_LOW</t>
+          <t>FOOD-BOILR-PH_LOW</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>COAL-BAN-FOOD-BOILR-WH_LOW</t>
+          <t>COAL-BAN-FOOD-BOILR-PH_LOW</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2095,17 +2095,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>-RESCOA</t>
+          <t>-INDCOA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JD-S_HEAT</t>
+          <t>FOOD-BOILR-WH_LOW</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>COAL-BAN-JD-S_HEAT</t>
+          <t>COAL-BAN-FOOD-BOILR-WH_LOW</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2137,17 +2137,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RESCOA</t>
+          <t>INDCOA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JD-S_HEAT</t>
+          <t>FOOD-BOILR-WH_LOW</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>COAL-BAN-JD-S_HEAT</t>
+          <t>COAL-BAN-FOOD-BOILR-WH_LOW</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2179,17 +2179,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>-INDCOA</t>
+          <t>-RESCOA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MEAT-BOILR-PH_INT</t>
+          <t>JD-S_HEAT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>COAL-BAN-MEAT-BOILR-PH_INT</t>
+          <t>COAL-BAN-JD-S_HEAT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2221,17 +2221,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>INDCOA</t>
+          <t>RESCOA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MEAT-BOILR-PH_INT</t>
+          <t>JD-S_HEAT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>COAL-BAN-MEAT-BOILR-PH_INT</t>
+          <t>COAL-BAN-JD-S_HEAT</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MEAT-BOILR-WH_LOW</t>
+          <t>MEAT-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>COAL-BAN-MEAT-BOILR-WH_LOW</t>
+          <t>COAL-BAN-MEAT-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2310,12 +2310,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MEAT-BOILR-WH_LOW</t>
+          <t>MEAT-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>COAL-BAN-MEAT-BOILR-WH_LOW</t>
+          <t>COAL-BAN-MEAT-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MINE-SH_LOW</t>
+          <t>MEAT-BOILR-WH_LOW</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>COAL-BAN-MINE-SH_LOW</t>
+          <t>COAL-BAN-MEAT-BOILR-WH_LOW</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MINE-SH_LOW</t>
+          <t>MEAT-BOILR-WH_LOW</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>COAL-BAN-MINE-SH_LOW</t>
+          <t>COAL-BAN-MEAT-BOILR-WH_LOW</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OTHR-BOILR-PH_INT</t>
+          <t>MINE-SH_LOW</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>COAL-BAN-OTHR-BOILR-PH_INT</t>
+          <t>COAL-BAN-MINE-SH_LOW</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>OTHR-BOILR-PH_INT</t>
+          <t>MINE-SH_LOW</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>COAL-BAN-OTHR-BOILR-PH_INT</t>
+          <t>COAL-BAN-MINE-SH_LOW</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OTHR-BOILR-PH_LOW</t>
+          <t>OTHR-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>COAL-BAN-OTHR-BOILR-PH_LOW</t>
+          <t>COAL-BAN-OTHR-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OTHR-BOILR-PH_LOW</t>
+          <t>OTHR-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>COAL-BAN-OTHR-BOILR-PH_LOW</t>
+          <t>COAL-BAN-OTHR-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PULP-BOILR-PH_INT</t>
+          <t>OTHR-BOILR-PH_LOW</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>COAL-BAN-PULP-BOILR-PH_INT</t>
+          <t>COAL-BAN-OTHR-BOILR-PH_LOW</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PULP-BOILR-PH_INT</t>
+          <t>OTHR-BOILR-PH_LOW</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>COAL-BAN-PULP-BOILR-PH_INT</t>
+          <t>COAL-BAN-OTHR-BOILR-PH_LOW</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2688,12 +2688,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WOOD-BOILR-PH_INT</t>
+          <t>PULP-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>COAL-BAN-WOOD-BOILR-PH_INT</t>
+          <t>COAL-BAN-PULP-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2730,35 +2730,119 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>PULP-BOILR-PH_INT</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>COAL-BAN-PULP-BOILR-PH_INT</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>-INDCOA</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>WOOD-BOILR-PH_INT</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>COAL-BAN-WOOD-BOILR-PH_INT</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>INDCOA</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>WOOD-BOILR-PH_INT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>COAL-BAN-WOOD-BOILR-PH_INT</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
